--- a/labeled/Add_Eating/July/multi_seed_results/seed_303/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_303/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,514 +442,514 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54.66666793823242</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
-        <v>50.65750503540039</v>
+        <v>49.89624404907227</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>40.20000076293945</v>
+        <v>34</v>
       </c>
       <c r="B3" t="n">
-        <v>22.17278861999512</v>
+        <v>19.65311813354492</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>58</v>
+        <v>9.809523582458496</v>
       </c>
       <c r="B4" t="n">
-        <v>53.33287048339844</v>
+        <v>54.77206039428711</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57.09999847412109</v>
+        <v>31.80952453613281</v>
       </c>
       <c r="B5" t="n">
-        <v>56.18051910400391</v>
+        <v>35.82839965820312</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>38.39373016357422</v>
+        <v>13.32027435302734</v>
       </c>
       <c r="B6" t="n">
-        <v>32.24574661254883</v>
+        <v>14.73616123199463</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>23</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B7" t="n">
-        <v>18.53157806396484</v>
+        <v>22.36260795593262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.938295841217041</v>
+        <v>25.46523094177246</v>
       </c>
       <c r="B8" t="n">
-        <v>14.25882911682129</v>
+        <v>25.39785575866699</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21.5475025177002</v>
+        <v>23.80952453613281</v>
       </c>
       <c r="B9" t="n">
-        <v>20.28659820556641</v>
+        <v>20.47437477111816</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10.34482765197754</v>
+        <v>34.09999847412109</v>
       </c>
       <c r="B10" t="n">
-        <v>12.9836540222168</v>
+        <v>30.21264457702637</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20.38095283508301</v>
+        <v>28.5</v>
       </c>
       <c r="B11" t="n">
-        <v>18.5899829864502</v>
+        <v>20.83221817016602</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10.91269874572754</v>
+        <v>18.55158805847168</v>
       </c>
       <c r="B12" t="n">
-        <v>13.42595767974854</v>
+        <v>15.11156749725342</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1.665034294128418</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="B13" t="n">
-        <v>8.099977493286133</v>
+        <v>50.74534225463867</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20.38095283508301</v>
+        <v>9.162561416625977</v>
       </c>
       <c r="B14" t="n">
-        <v>18.5899829864502</v>
+        <v>7.2640061378479</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>27.23809432983398</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B15" t="n">
-        <v>20.30147171020508</v>
+        <v>21.39618301391602</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13.88888931274414</v>
+        <v>25.75905990600586</v>
       </c>
       <c r="B16" t="n">
-        <v>12.4059419631958</v>
+        <v>27.10136795043945</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>42.90000152587891</v>
+        <v>15.90476226806641</v>
       </c>
       <c r="B17" t="n">
-        <v>39.06467819213867</v>
+        <v>20.17432022094727</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>39.78174591064453</v>
       </c>
       <c r="B18" t="n">
-        <v>29.6942138671875</v>
+        <v>44.92462158203125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24.87757110595703</v>
+        <v>14.6245059967041</v>
       </c>
       <c r="B19" t="n">
-        <v>24.58035278320312</v>
+        <v>20.34784698486328</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>29.90476226806641</v>
+        <v>22.51984214782715</v>
       </c>
       <c r="B20" t="n">
-        <v>20.79969596862793</v>
+        <v>29.19874382019043</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>29.10000038146973</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="B21" t="n">
-        <v>24.69512557983398</v>
+        <v>25.30898475646973</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>41.20000076293945</v>
+        <v>17.23800277709961</v>
       </c>
       <c r="B22" t="n">
-        <v>40.09902572631836</v>
+        <v>16.52152252197266</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>27.6785717010498</v>
+        <v>2.938295841217041</v>
       </c>
       <c r="B23" t="n">
-        <v>23.91686058044434</v>
+        <v>11.11029052734375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14.18650817871094</v>
+        <v>40.59999847412109</v>
       </c>
       <c r="B24" t="n">
-        <v>13.74717617034912</v>
+        <v>37.24007797241211</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15.51383399963379</v>
+        <v>33.5</v>
       </c>
       <c r="B25" t="n">
-        <v>19.38504600524902</v>
+        <v>28.95763206481934</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>13.89999961853027</v>
+        <v>31.63565063476562</v>
       </c>
       <c r="B26" t="n">
-        <v>12.3906364440918</v>
+        <v>24.3347339630127</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20.83333396911621</v>
+        <v>11</v>
       </c>
       <c r="B27" t="n">
-        <v>20.56614303588867</v>
+        <v>16.90231323242188</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>68.28571319580078</v>
+        <v>57.78648376464844</v>
       </c>
       <c r="B28" t="n">
-        <v>58.91099548339844</v>
+        <v>21.02794075012207</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>40.27777862548828</v>
+        <v>20.47012710571289</v>
       </c>
       <c r="B29" t="n">
-        <v>33.08759307861328</v>
+        <v>25.5136604309082</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17.46031761169434</v>
+        <v>12.30158710479736</v>
       </c>
       <c r="B30" t="n">
-        <v>22.15130424499512</v>
+        <v>14.59824657440186</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>68.28571319580078</v>
+        <v>10.4761905670166</v>
       </c>
       <c r="B31" t="n">
-        <v>58.91099548339844</v>
+        <v>16.42245674133301</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>58.76591491699219</v>
+        <v>12.99603176116943</v>
       </c>
       <c r="B32" t="n">
-        <v>58.28612899780273</v>
+        <v>44.10958480834961</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>80</v>
+        <v>9.5</v>
       </c>
       <c r="B33" t="n">
-        <v>69.24243927001953</v>
+        <v>44.17234420776367</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>19.84127044677734</v>
+        <v>9.189723014831543</v>
       </c>
       <c r="B34" t="n">
-        <v>30.35034370422363</v>
+        <v>9.4456787109375</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>60.82272338867188</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="B35" t="n">
-        <v>58.52547454833984</v>
+        <v>13.78015899658203</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>25.6611156463623</v>
+        <v>28.7952995300293</v>
       </c>
       <c r="B36" t="n">
-        <v>24.58148193359375</v>
+        <v>39.13784408569336</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>24.50396919250488</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="B37" t="n">
-        <v>22.6767635345459</v>
+        <v>18.45989227294922</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>85.69999694824219</v>
+        <v>6.0724778175354</v>
       </c>
       <c r="B38" t="n">
-        <v>81.81741333007812</v>
+        <v>19.47200965881348</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>9.162561416625977</v>
+        <v>10.91269874572754</v>
       </c>
       <c r="B39" t="n">
-        <v>6.291249752044678</v>
+        <v>18.4565258026123</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20.33730125427246</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="B40" t="n">
-        <v>20.78264999389648</v>
+        <v>19.10592651367188</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>38.09999847412109</v>
+        <v>30.55827713012695</v>
       </c>
       <c r="B41" t="n">
-        <v>38.70979309082031</v>
+        <v>32.40305328369141</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>5.221674919128418</v>
+        <v>20.83333396911621</v>
       </c>
       <c r="B42" t="n">
-        <v>5.674605846405029</v>
+        <v>20.41754531860352</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11.65524005889893</v>
+        <v>26.28968238830566</v>
       </c>
       <c r="B43" t="n">
-        <v>13.59505939483643</v>
+        <v>26.464111328125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>9.189723014831543</v>
+        <v>22.33104705810547</v>
       </c>
       <c r="B44" t="n">
-        <v>7.658459663391113</v>
+        <v>20.78032875061035</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>30.19047546386719</v>
+        <v>16.35651397705078</v>
       </c>
       <c r="B45" t="n">
-        <v>22.54460525512695</v>
+        <v>17.34722709655762</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15.08875751495361</v>
+        <v>10.7737512588501</v>
       </c>
       <c r="B46" t="n">
-        <v>16.41559791564941</v>
+        <v>11.19761180877686</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>13.32027435302734</v>
+        <v>62.09523773193359</v>
       </c>
       <c r="B47" t="n">
-        <v>14.92131233215332</v>
+        <v>59.28538513183594</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>11.11111068725586</v>
+        <v>19</v>
       </c>
       <c r="B48" t="n">
-        <v>11.79296588897705</v>
+        <v>18.55934715270996</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>97.94319152832031</v>
+        <v>10.85714244842529</v>
       </c>
       <c r="B49" t="n">
-        <v>95.50598907470703</v>
+        <v>20.35624694824219</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>46.20000076293945</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="B50" t="n">
-        <v>29.22013664245605</v>
+        <v>25.26125144958496</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>30.15872955322266</v>
+        <v>24.38785552978516</v>
       </c>
       <c r="B51" t="n">
-        <v>24.24801254272461</v>
+        <v>18.0942325592041</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>26.28968238830566</v>
+        <v>10.47992134094238</v>
       </c>
       <c r="B52" t="n">
-        <v>20.04204559326172</v>
+        <v>14.92837810516357</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>22.9187068939209</v>
+        <v>16.96428489685059</v>
       </c>
       <c r="B53" t="n">
-        <v>14.85002136230469</v>
+        <v>10.25929641723633</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>20.33730125427246</v>
+        <v>45</v>
       </c>
       <c r="B54" t="n">
-        <v>21.88831520080566</v>
+        <v>36.56997680664062</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>25.09920692443848</v>
+        <v>36.23898315429688</v>
       </c>
       <c r="B55" t="n">
-        <v>22.88464736938477</v>
+        <v>19.17533683776855</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>36</v>
+        <v>34.20000076293945</v>
       </c>
       <c r="B56" t="n">
-        <v>34.90771102905273</v>
+        <v>28.28290939331055</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>53.20000076293945</v>
+        <v>18.4761905670166</v>
       </c>
       <c r="B57" t="n">
-        <v>51.17638778686523</v>
+        <v>24.67370986938477</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>19.84127044677734</v>
+        <v>8.630952835083008</v>
       </c>
       <c r="B58" t="n">
-        <v>16.94215774536133</v>
+        <v>10.35614585876465</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129.3000030517578</v>
+        <v>21.84133148193359</v>
       </c>
       <c r="B59" t="n">
-        <v>128.6269226074219</v>
+        <v>23.27048492431641</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>36.29999923706055</v>
+        <v>10.77075099945068</v>
       </c>
       <c r="B60" t="n">
-        <v>39.46536636352539</v>
+        <v>14.77943515777588</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>5.320197105407715</v>
+        <v>23.21428489685059</v>
       </c>
       <c r="B61" t="n">
-        <v>11.85202693939209</v>
+        <v>18.35544395446777</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>23.10000038146973</v>
+        <v>6.547618865966797</v>
       </c>
       <c r="B62" t="n">
-        <v>22.49432563781738</v>
+        <v>8.557540893554688</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>24.5714282989502</v>
+        <v>18.51126289367676</v>
       </c>
       <c r="B63" t="n">
-        <v>24.35837364196777</v>
+        <v>26.55677795410156</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>36.29999923706055</v>
+        <v>22.09523773193359</v>
       </c>
       <c r="B64" t="n">
-        <v>39.46536636352539</v>
+        <v>50.22952270507812</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>13.71204662322998</v>
+        <v>11.56126499176025</v>
       </c>
       <c r="B65" t="n">
-        <v>13.11155414581299</v>
+        <v>40.15427017211914</v>
       </c>
     </row>
     <row r="66">
@@ -957,647 +957,231 @@
         <v>26.15083312988281</v>
       </c>
       <c r="B66" t="n">
-        <v>28.59819030761719</v>
+        <v>29.1479434967041</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>40</v>
+        <v>15.57539653778076</v>
       </c>
       <c r="B67" t="n">
-        <v>32.93960571289062</v>
+        <v>20.76815032958984</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>63.17335891723633</v>
+        <v>34.5</v>
       </c>
       <c r="B68" t="n">
-        <v>58.20157241821289</v>
+        <v>28.49279403686523</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>11.70634937286377</v>
+        <v>27.32615089416504</v>
       </c>
       <c r="B69" t="n">
-        <v>12.86243057250977</v>
+        <v>26.63358879089355</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>19.84127044677734</v>
+        <v>24.50396919250488</v>
       </c>
       <c r="B70" t="n">
-        <v>24.06660652160645</v>
+        <v>20.91144180297852</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>19.74206352233887</v>
+        <v>17.94871711730957</v>
       </c>
       <c r="B71" t="n">
-        <v>12.66033840179443</v>
+        <v>15.13488388061523</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>35.5</v>
+        <v>19.74206352233887</v>
       </c>
       <c r="B72" t="n">
-        <v>28.49584007263184</v>
+        <v>10.62147521972656</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>25.95494651794434</v>
+        <v>24.19047546386719</v>
       </c>
       <c r="B73" t="n">
-        <v>26.15307235717773</v>
+        <v>26.46405982971191</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>13.32027435302734</v>
+        <v>7.242063522338867</v>
       </c>
       <c r="B74" t="n">
-        <v>14.92131233215332</v>
+        <v>10.53248596191406</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>97.94319152832031</v>
+        <v>92.90000152587891</v>
       </c>
       <c r="B75" t="n">
-        <v>96.04372406005859</v>
+        <v>86.56501007080078</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>25.46523094177246</v>
+        <v>46.79999923706055</v>
       </c>
       <c r="B76" t="n">
-        <v>26.83309173583984</v>
+        <v>47.84381866455078</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>85.69999694824219</v>
+        <v>28.10000038146973</v>
       </c>
       <c r="B77" t="n">
-        <v>81.81741333007812</v>
+        <v>25.68281745910645</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>30.85210609436035</v>
+        <v>9.486166000366211</v>
       </c>
       <c r="B78" t="n">
-        <v>27.10149955749512</v>
+        <v>19.64375305175781</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>28.5</v>
+        <v>14.20176315307617</v>
       </c>
       <c r="B79" t="n">
-        <v>24.3615550994873</v>
+        <v>19.70123863220215</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>18.55158805847168</v>
+        <v>57</v>
       </c>
       <c r="B80" t="n">
-        <v>12.98737907409668</v>
+        <v>53.77036285400391</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>54.29999923706055</v>
+        <v>39</v>
       </c>
       <c r="B81" t="n">
-        <v>52.93494033813477</v>
+        <v>36.58043670654297</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>78.35455322265625</v>
+        <v>26.34671974182129</v>
       </c>
       <c r="B82" t="n">
-        <v>75.97171020507812</v>
+        <v>24.31032180786133</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>25.75905990600586</v>
+        <v>14.6245059967041</v>
       </c>
       <c r="B83" t="n">
-        <v>25.26272964477539</v>
+        <v>12.21438789367676</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>68.5</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B84" t="n">
-        <v>63.42814636230469</v>
+        <v>25.94375228881836</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>46.20000076293945</v>
+        <v>23.5238094329834</v>
       </c>
       <c r="B85" t="n">
-        <v>29.22013664245605</v>
+        <v>32.04144668579102</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>22.51984214782715</v>
+        <v>9.304603576660156</v>
       </c>
       <c r="B86" t="n">
-        <v>20.31271743774414</v>
+        <v>12.60594749450684</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>99.20635223388672</v>
+        <v>10.7619047164917</v>
       </c>
       <c r="B87" t="n">
-        <v>97.98062133789062</v>
+        <v>12.88567924499512</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2.938295841217041</v>
+        <v>59.40000152587891</v>
       </c>
       <c r="B88" t="n">
-        <v>14.25882911682129</v>
+        <v>58.42100524902344</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>31.80952453613281</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B89" t="n">
-        <v>30.61221694946289</v>
+        <v>24.7794017791748</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>6.547618865966797</v>
+        <v>42.09999847412109</v>
       </c>
       <c r="B90" t="n">
-        <v>7.784085750579834</v>
+        <v>29.13379669189453</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>58.70000076293945</v>
+        <v>31.29999923706055</v>
       </c>
       <c r="B91" t="n">
-        <v>58.626220703125</v>
+        <v>31.77506828308105</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>7.242063522338867</v>
+        <v>12.73261547088623</v>
       </c>
       <c r="B92" t="n">
-        <v>5.199184894561768</v>
+        <v>9.59339714050293</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>80.69999694824219</v>
+        <v>46.20000076293945</v>
       </c>
       <c r="B93" t="n">
-        <v>77.04786682128906</v>
+        <v>33.63820648193359</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>39.17727661132812</v>
+        <v>13.2380952835083</v>
       </c>
       <c r="B94" t="n">
-        <v>40.23046493530273</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>9.189723014831543</v>
-      </c>
-      <c r="B95" t="n">
-        <v>7.658459663391113</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>40</v>
-      </c>
-      <c r="B96" t="n">
-        <v>55.31066131591797</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>28.7952995300293</v>
-      </c>
-      <c r="B97" t="n">
-        <v>26.15961074829102</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>6.0724778175354</v>
-      </c>
-      <c r="B98" t="n">
-        <v>11.80277156829834</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>78.90000152587891</v>
-      </c>
-      <c r="B99" t="n">
-        <v>79.83061218261719</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>59.40000152587891</v>
-      </c>
-      <c r="B100" t="n">
-        <v>51.54839324951172</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>20.83333396911621</v>
-      </c>
-      <c r="B101" t="n">
-        <v>20.56614303588867</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>26.10000038146973</v>
-      </c>
-      <c r="B102" t="n">
-        <v>16.33213233947754</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>31.80952453613281</v>
-      </c>
-      <c r="B103" t="n">
-        <v>25.10091781616211</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>14.22924900054932</v>
-      </c>
-      <c r="B104" t="n">
-        <v>13.96916961669922</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>10.7737512588501</v>
-      </c>
-      <c r="B105" t="n">
-        <v>10.71557235717773</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>35.90000152587891</v>
-      </c>
-      <c r="B106" t="n">
-        <v>31.49199867248535</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>20.53571510314941</v>
-      </c>
-      <c r="B107" t="n">
-        <v>23.79863739013672</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>61.90476226806641</v>
-      </c>
-      <c r="B108" t="n">
-        <v>57.27180862426758</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>79.36508178710938</v>
-      </c>
-      <c r="B109" t="n">
-        <v>73.36809539794922</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>10.47992134094238</v>
-      </c>
-      <c r="B110" t="n">
-        <v>16.9136905670166</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>6.502462863922119</v>
-      </c>
-      <c r="B111" t="n">
-        <v>4.521045684814453</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>36.23898315429688</v>
-      </c>
-      <c r="B112" t="n">
-        <v>36.05815887451172</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>26.28968238830566</v>
-      </c>
-      <c r="B113" t="n">
-        <v>20.04204559326172</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>18.4761905670166</v>
-      </c>
-      <c r="B114" t="n">
-        <v>17.33475494384766</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>21.84133148193359</v>
-      </c>
-      <c r="B115" t="n">
-        <v>21.15774536132812</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>22.3214282989502</v>
-      </c>
-      <c r="B116" t="n">
-        <v>21.88625335693359</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>35.29999923706055</v>
-      </c>
-      <c r="B117" t="n">
-        <v>28.05808448791504</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>22.09523773193359</v>
-      </c>
-      <c r="B118" t="n">
-        <v>26.91879844665527</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>11.56126499176025</v>
-      </c>
-      <c r="B119" t="n">
-        <v>17.02305793762207</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>26.15083312988281</v>
-      </c>
-      <c r="B120" t="n">
-        <v>28.59819030761719</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>23.80952453613281</v>
-      </c>
-      <c r="B121" t="n">
-        <v>15.33633518218994</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="B122" t="n">
-        <v>20.42571258544922</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>79.36508178710938</v>
-      </c>
-      <c r="B123" t="n">
-        <v>78.12203216552734</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>17.94871711730957</v>
-      </c>
-      <c r="B124" t="n">
-        <v>15.11456203460693</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>19.74206352233887</v>
-      </c>
-      <c r="B125" t="n">
-        <v>12.66033840179443</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>59.52381134033203</v>
-      </c>
-      <c r="B126" t="n">
-        <v>58.21295547485352</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>34.70000076293945</v>
-      </c>
-      <c r="B127" t="n">
-        <v>21.63268089294434</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>40.47618865966797</v>
-      </c>
-      <c r="B128" t="n">
-        <v>33.37614440917969</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>92.90000152587891</v>
-      </c>
-      <c r="B129" t="n">
-        <v>93.18225860595703</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>11.11111068725586</v>
-      </c>
-      <c r="B130" t="n">
-        <v>11.79296588897705</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>9.486166000366211</v>
-      </c>
-      <c r="B131" t="n">
-        <v>6.270687103271484</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>14.20176315307617</v>
-      </c>
-      <c r="B132" t="n">
-        <v>15.75107097625732</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>12.69841289520264</v>
-      </c>
-      <c r="B133" t="n">
-        <v>15.21775054931641</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>20.4761905670166</v>
-      </c>
-      <c r="B134" t="n">
-        <v>33.14382553100586</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>44.70000076293945</v>
-      </c>
-      <c r="B135" t="n">
-        <v>39.10875701904297</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>11.4285717010498</v>
-      </c>
-      <c r="B136" t="n">
-        <v>11.53818035125732</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>23.5238094329834</v>
-      </c>
-      <c r="B137" t="n">
-        <v>27.04294776916504</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>14.20176315307617</v>
-      </c>
-      <c r="B138" t="n">
-        <v>15.75107097625732</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>21.82539749145508</v>
-      </c>
-      <c r="B139" t="n">
-        <v>22.27532196044922</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>26.44466209411621</v>
-      </c>
-      <c r="B140" t="n">
-        <v>23.62773323059082</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>34.02777862548828</v>
-      </c>
-      <c r="B141" t="n">
-        <v>26.11889266967773</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>24.5714282989502</v>
-      </c>
-      <c r="B142" t="n">
-        <v>24.35837364196777</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>34.37805938720703</v>
-      </c>
-      <c r="B143" t="n">
-        <v>17.97800636291504</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>131.6999969482422</v>
-      </c>
-      <c r="B144" t="n">
-        <v>123.7098083496094</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>21.5475025177002</v>
-      </c>
-      <c r="B145" t="n">
-        <v>20.35129356384277</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>44.57143020629883</v>
-      </c>
-      <c r="B146" t="n">
-        <v>42.62794494628906</v>
+        <v>28.46146392822266</v>
       </c>
     </row>
   </sheetData>
